--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T15:54:27+00:00</t>
+    <t>2026-01-30T10:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:12:59+00:00</t>
+    <t>2026-03-09T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:22:43+00:00</t>
+    <t>2026-03-17T11:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:12:47+00:00</t>
+    <t>2026-03-23T15:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:20:38+00:00</t>
+    <t>2026-03-24T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-1</t>
+    <t>0.7.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:51:35+00:00</t>
+    <t>2026-03-24T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -371,7 +371,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -507,7 +507,7 @@
     <t>Task.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -547,7 +547,7 @@
     <t>Task.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -836,7 +836,7 @@
     <t>Task.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1053,7 +1053,7 @@
     <t>The type(s) of task performers allowed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
+    <t>http://hl7.org/fhir/ValueSet/performer-role|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.role, Request.performerType</t>
@@ -1167,7 +1167,7 @@
     <t>Task.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -1215,7 +1215,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -2024,15 +2024,15 @@
   <dimension ref="A1:AN109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.05859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.42578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.68359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.48828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="27.80078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2043,26 +2043,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="169.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="102.80859375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="43.2734375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="145.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="88.13671875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="37.1015625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="55.72265625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="109.98828125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="62.87890625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="47.7734375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="94.296875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="53.91015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3211,7 +3211,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>148</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>191</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>210</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>236</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>244</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>249</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>288</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>297</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>305</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>314</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>320</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>337</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>354</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>443</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>452</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>461</v>
       </c>
@@ -10423,7 +10423,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>470</v>
       </c>
@@ -11109,7 +11109,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>480</v>
       </c>
@@ -11795,7 +11795,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>489</v>
       </c>
@@ -13167,7 +13167,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>515</v>
       </c>
@@ -13855,7 +13855,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>524</v>
       </c>
@@ -14545,12 +14545,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN109">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-task.xlsx
+++ b/main/ig/StructureDefinition-ror-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
